--- a/data_extactor/batch_10_fa/batch_0076_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0076_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACCA Manual J | Abraxas Energy Consulting Metrix | Adobe Photoshop | Architectural Energy Corporation ENFORMA Building Diagnostics | Architectural Energy Corporation REM/Rate | Autodesk AutoCAD | C++ | Cool Roof Calculator | DesignBuilder Software DesignBuilder | EffTec EffTrack | Ekotrope RATER | Elite Software Energy Audit | Enercom Energy Depot for Business | Enercom Energy Depot for Homes | Energy Efficient Rehab Advisor | EnergyPlus | Esri ArcGIS | Facility Energy Decision Systems FEDS | Federal Renewable Energy Screening Assistant FRESA | Fielding Data Labs OptoMizer | Fundamental Objects foAudits | Good Steward Software EnergyCAP | Home Energy Efficient Design HEED | IBM SPSS Statistics | InterEnergy Software Building Energy Analyzer PRO | Itron Enterprise Energy Management EEM Suite | Linux | Microsoft .NET Framework | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint | Microsoft Visual Basic | Microsoft Visual FoxPro | Microsoft Word | MotorMaster+ | Onset Computer Corporation HOBOware | Performance Systems Development TREAT | Program for Energy Analysis of Residences PEAR | نرم‌افزار نمودار سایکرومتریک | Python | R | REScheck | Retrofit Energy Savings Estimation Model RESEM | نرم‌افزار SAP | SAS | نرم‌افزار Salesforce | Snugg Home Snugg Pro | Structured query language SQL | The MathWorks MATLAB | The Weatherization Assistant | Trane TRACE | UNIX | نرم‌افزار مرورگر وب | Wolfram Research Mathematica | dBASE</t>
+          <t>ACCA Manual J | Abraxas Energy Consulting Metrix | Adobe Photoshop | Architectural Energy Corporation ENFORMA Building Diagnostics | Architectural Energy Corporation REM/Rate | Autodesk AutoCAD | C++ | Cool Roof Calculator | DesignBuilder Software DesignBuilder | EffTec EffTrack | Ekotrope RATER | Elite Software Energy Audit | Enercom Energy Depot for Business | Enercom Energy Depot for Homes | Energy Efficient Rehab Advisor | EnergyPlus | Esri ArcGIS | Facility Energy Decision Systems FEDS | Federal Renewable Energy Screening Assistant FRESA | Fielding Data Labs OptoMizer | Fundamental Objects foAudits | Good Steward Software EnergyCAP | Home Energy Efficient Design HEED | IBM SPSS Statistics | InterEnergy Software Building Energy Analyzer PRO | Itron Enterprise Energy Management EEM Suite | Linux | Microsoft .NET Framework | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint | Microsoft Visual Basic | Microsoft Visual FoxPro | Microsoft Word | MotorMaster+ | Onset Computer Corporation HOBOware | Performance Systems Development TREAT | Program for Energy Analysis of Residences PEAR | نرم‌افزار نمودار سایکرومتریک | Python | R | REScheck | Retrofit Energy Savings Estimation Model RESEM | نرم‌افزار SAP | SAS | نرم‌افزار Salesforce | Snugg Home Snugg Pro | زبان پرس‌وجوی ساختاریافته SQL | The MathWorks MATLAB | The Weatherization Assistant | Trane TRACE | UNIX | نرم‌افزار مرورگر وب | Wolfram Research Mathematica | dBASE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن‌گفتن | گوش‌دادن فعال | تفکر انتقادی | نگارش | ریاضیات | پایش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | ریاضیات | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | ساختمان و ساخت‌وساز | ریاضیات | مهندسی و فناوری | مکانیک | فیزیک | زبان انگلیسی | فروش و بازاریابی | طراحی | کامپیوتر و الکترونیک | آموزش و پرورش</t>
+          <t>خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | ریاضیات | مهندسی و فناوری | مکانیک | فیزیک | زبان انگلیسی | فروش و بازاریابی | طراحی | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | استدلال ریاضی | بینایی نزدیک | سهولت در کار با اعداد | ترتیب‌دهی به اطلاعات | روان بودن ایده‌ها | انعطاف‌پذیری بستار | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | تجسم | سرعت ادراکی | سرعت بستار | اصالت | بینایی دور | دقت کنترل</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | استدلال ریاضی | بینایی نزدیک | توانایی عددی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری بستار | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | تجسم | سرعت ادراکی | سرعت بستار | اصالت | بینایی دور | دقت کنترل</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | فشار زمانی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سروکار داشتن با مشتریان خارجی یا عموم مردم | فضای باز، در معرض تمام شرایط آب و هوایی | فضای بسته، با دمای کنترل‌شده | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | در معرض شرایط نوری بسیار روشن یا ناکافی | فضای بسته، بدون دمای کنترل‌شده</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | فشار زمانی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعامل با مشتریان خارجی یا عموم مردم | فضای باز، در معرض تمام شرایط آب و هوایی | محیط داخلی، دارای کنترل شرایط محیطی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | محیط داخلی، بدون کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | مدیران نیروگاه‌های زیست‌توده | بازرسان ساخت‌وساز و ساختمان | مهندسان انرژی، به جز باد و خورشید | تکنولوژیست‌ها و تکنسین‌های مهندسی محیط زیست | مدیران تولید زمین‌گرمایی | اکولوژیست‌های صنعتی | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | توزیع‌کنندگان و دیسپچرهای برق | مدیران نصب انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | نصابان خورشیدی فتوولتائیک | نمایندگان فروش و ارزیابان خورشیدی | متخصصان پایداری | مهندسان آب/فاضلاب | نصابان و تکنسین‌های عایق‌سازی و مقاوم‌سازی در برابر شرایط جوی | مدیران توسعه انرژی بادی | مهندسان انرژی بادی | تکنسین‌های خدمات توربین بادی</t>
+          <t>مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | مدیران نیروگاه‌های زیست‌توده | بازرسان ساختمان و ساخت‌وساز | مهندسان انرژی، به جز باد و خورشید | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مدیران تولید زمین‌گرمایی | بوم‌شناسان صنعتی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | توزیع‌کنندگان و دیسپچرهای برق | مدیران نصب انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های فتوولتائیک خورشیدی | نمایندگان و ارزیابان فروش تجهیزات خورشیدی | متخصصان پایداری | مهندسان آب و فاضلاب | نصابان و تکنسین‌های عایق‌سازی و مقاوم‌سازی در برابر شرایط جوی | مدیران توسعه انرژی بادی | مهندسان انرژی بادی | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Computerized maintenance management system CMMS | Elevator Controls INTERACT | Microsoft Excel | Microsoft Outlook | Microsoft Word | نرم‌افزار زمان‌بندی | نرم‌افزار عیب‌یابی | WORLD Electronics Freedomware</t>
+          <t>سیستم مدیریت نگهداری کامپیوتری CMMS | Elevator Controls INTERACT | Microsoft Excel | Microsoft Outlook | Microsoft Word | نرم‌افزار زمان‌بندی | نرم‌افزار عیب‌یابی | WORLD Electronics Freedomware</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش‌دادن فعال | درک مطلب | یادگیری فعال | پایش | سخن‌گفتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و شخصی | ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | کامپیوتر و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | مدیریت و اداره امور</t>
+          <t>مکانیک | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | حساسیت به مسئله | زبردستی دستی | درک شفاهی | بینایی نزدیک | زبردستی انگشتان | ثبات بازو-دست | استدلال استقرایی | ترتیب‌دهی به اطلاعات | انعطاف‌پذیری دامنه حرکت | تجسم | دقت کنترل | بیان شفاهی | بیان کتبی | درک کتبی | تعادل کلی بدن | قدرت تنه | زمان عکس‌العمل | هماهنگی چند عضو | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | توجه انتخابی</t>
+          <t>استدلال قیاسی | حساسیت به مسئله | مهارت دستی | درک شفاهی | بینایی نزدیک | مهارت انگشتان | ثبات دست و بازو | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دامنه حرکت | تجسم | دقت کنترل | بیان شفاهی | بیان کتبی | درک کتبی | تعادل کلی بدن | قدرت تنه | زمان عکس‌العمل | هماهنگی چند عضو | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>فراوانی تصمیم‌گیری | در معرض شرایط خطرناک بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | ایمیل | بهداشت و ایمنی سایر کارگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت | در معرض ارتفاعات بالا بودن | در معرض فضای کاری تنگ، موقعیت‌های نامناسب بودن | پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | در معرض شرایط نوری بسیار روشن یا ناکافی | صرف زمان برای خم شدن یا چرخاندن بدن | در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده بودن | فضای بسته، با دمای کنترل‌شده | سروکار داشتن با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | در معرض تجهیزات خطرناک بودن | پیامد خطا | در معرض آلاینده‌ها بودن | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | تعیین وظایف، اولویت‌ها و اهداف | در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها بودن | پیامدهای کاری و نتایج سایر کارگران | فشار زمانی | صرف زمان به صورت ایستاده | آزادی در تصمیم‌گیری | هماهنگ‌کردن یا هدایت دیگران در انجام فعالیت‌های کاری | سروکار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | در معرض دمای بسیار گرم یا سرد بودن | فضای بسته، بدون دمای کنترل‌شده | کار با یا مشارکت در یک گروه کاری یا تیم | سطح رقابت | اهمیت تکرار وظایف مشابه | نزدیکی فیزیکی | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای انجام حرکات تکراری | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن</t>
+          <t>فراوانی تصمیم‌گیری | قرار گرفتن در معرض شرایط خطرناک | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | ایمیل | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض ارتفاعات بالا | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | قرار گرفتن در معرض تجهیزات خطرناک | پیامد خطا | قرار گرفتن در معرض آلاینده‌ها | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامدهای کاری و نتایج سایر کارکنان | فشار زمانی | صرف زمان برای ایستادن | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | محیط داخلی، بدون کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | سطح رقابت | اهمیت تکرار وظایف یکسان | نزدیکی فیزیکی | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای انجام حرکات تکراری | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان ساختار، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | نصابان و تعمیرکاران خطوط انتقال نیروی برق | نصابان و تعمیرکاران الکتریکی و الکترونیکی، تجهیزات حمل و نقل | مونتاژکنندگان موتور و سایر ماشین‌آلات | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | دستیاران--کارگران نصب، تعمیر و نگهداری | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری، عمومی | تعمیرکاران درب‌های مکانیکی | سازندگان آسیاب و نصابان ماشین‌آلات صنعتی (Millwrights) | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | لوله‌کشان، لوله‌کشان صنعتی و لوله‌کشان بخار | تعمیرکاران واگن‌های ریلی | ریگرها (دکل‌بندها) | کارگران آهن و فولاد ساختمانی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصابان و تعمیرکاران خطوط انتقال نیروی برق | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | دستیاران--کارگران نصب، نگهداری و تعمیرات | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری و تعمیرات عمومی | تعمیرکاران درب‌های مکانیکی | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | تعمیرکنندگان واگن‌های ریلی | ریگرها | کارگران سازه‌های آهنی و فولادی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>سازنده حصار | پیمانکار حصار | نصاب حصار | کارگر حصار | مکانیک حصار | تکنسین حصار | تکنسین دروازه | نصاب حصار چوبی</t>
+          <t>سازنده حصار | پیمانکار حصار | نصاب حصار | نصب‌کننده حصار | کارگر حصار | مکانیک حصار | تکنسین حصار (Fence Tech) | تکنسین دروازه (Gate Tech) | نصاب حصار چوبی</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>پایش | تفکر انتقادی | سخن‌گفتن | گوش‌دادن فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | ساختمان و ساخت‌وساز | ترابری | مدیریت و اداره امور | طراحی | ریاضیات | زبان انگلیسی | آموزش و پرورش | مکانیک | فروش و بازاریابی | تولید و فرآوری | مهندسی و فناوری | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | حمل و نقل | مدیریت و اداره | طراحی | ریاضیات | زبان انگلیسی | آموزش و پرورش | مکانیک | فروش و بازاریابی | تولید و فرآوری | مهندسی و فناوری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>قدرت تنه | زبردستی دستی | هماهنگی چند عضو | قدرت ایستا | ثبات بازو-دست | زبردستی انگشتان | دقت کنترل | ترتیب‌دهی به اطلاعات | بینایی نزدیک | استقامت | قدرت پویا | تشخیص گفتار | درک عمق | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
+          <t>قدرت تنه | مهارت دستی | هماهنگی چند عضو | قدرت ایستا | ثبات دست و بازو | مهارت انگشتان | دقت کنترل | ترتیب‌دهی اطلاعات | بینایی نزدیک | استقامت | قدرت پویا | تشخیص گفتار | درک عمق | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | بهداشت و ایمنی سایر کارگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | پیامدهای کاری و نتایج سایر کارگران | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان به صورت ایستاده | مکالمات تلفنی | در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده بودن | ارتباط با دیگران | در معرض تجهیزات خطرناک بودن | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | پیامد خطا | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای خم شدن یا چرخاندن بدن | نزدیکی فیزیکی | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | در معرض ارتفاعات بالا بودن | در معرض دمای بسیار گرم یا سرد بودن | هماهنگ‌کردن یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | در یک وسیله نقلیه روباز یا کار با تجهیزات روباز | سروکار داشتن با مشتریان خارجی یا عموم مردم | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | پیامدهای کاری و نتایج سایر کارکنان | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای ایستادن | مکالمات تلفنی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | ارتباط با دیگران | قرار گرفتن در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | پیامد خطا | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای خم کردن یا چرخاندن بدن | نزدیکی فیزیکی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض ارتفاعات بالا | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | در یک وسیله نقلیه روباز یا کار با تجهیزات | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>نجاران | بناهای سیمان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | نصابان و تعمیرکاران خطوط انتقال نیروی برق | برق‌کاران | دستیاران--نجاران | دستیاران--برق‌کاران | دستیاران--لوله‌گذاران، لوله‌کشان، لوله‌کشان صنعتی و لوله‌کشان بخار | کارگران عایق‌کاری، کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | کارگران شابلون‌زنی و نشانه‌گذاری، فلز و پلاستیک | تعمیرکاران درب‌های مکانیکی | لوله‌گذاران | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | کارگران آهن‌آلات تقویتی و میلگردکاران | سقف‌کاران | کارگران ورق‌کار فلزی | کارگران آهن و فولاد ساختمانی | سازندگان و مونتاژکنندگان قطعات فلزی ساختمانی</t>
+          <t>نجّاران | بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | نصابان و تعمیرکاران خطوط انتقال نیروی برق | برق‌کاران | دستیاران--نجاران | دستیاران--برق‌کاران | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | کارگران شابلون‌زنی، فلز و پلاستیک | تعمیرکاران درب‌های مکانیکی | لوله‌گذاران | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | کارگران آهن تقویتی و میلگرد | سقف‌سازان | کارگران ورق‌کاری | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکاران فلزات سازه‌ای</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Computerized maintenance management system software CMMS | Database software | Inventory management systems | Jenkins CI | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار SAP | Xactware Xactimate</t>
+          <t>Computerized maintenance management system software CMMS | نرم‌افزار پایگاه داده | سیستم‌های مدیریت موجودی | Jenkins CI | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار SAP | Xactware Xactimate</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>پایش | تفکر انتقادی | گوش‌دادن فعال | درک مطلب | سخن‌گفتن | یادگیری فعال | نگارش</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مدیریت و اداره امور | ترابری | خدمات مشتریان و شخصی | ساختمان و ساخت‌وساز | مکانیک | زبان انگلیسی</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره | حمل و نقل | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | مکانیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | دقت کنترل | بینایی نزدیک | بیان شفاهی | تشخیص گفتار | ثبات بازو-دست | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان کتبی | هماهنگی چند عضو | ترتیب‌دهی به اطلاعات | استدلال استقرایی | تجسم | زبردستی دستی | وضوح گفتار | درک کتبی | انعطاف‌پذیری دامنه حرکت | توجه انتخابی | بینایی دور | قدرت ایستا | زبردستی انگشتان | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>حساسیت به مسئله | درک شفاهی | دقت کنترل | بینایی نزدیک | بیان شفاهی | تشخیص گفتار | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان کتبی | هماهنگی چند عضو | ترتیب‌دهی اطلاعات | استدلال استقرایی | تجسم | مهارت دستی | وضوح گفتار | درک کتبی | انعطاف‌پذیری دامنه حرکت | توجه انتخابی | بینایی دور | قدرت ایستا | مهارت انگشتان | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | پوشیدن تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | بهداشت و ایمنی سایر کارگران | در معرض آلاینده‌ها بودن | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | فشار زمانی | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارگران | فضای بسته، بدون دمای کنترل‌شده | نزدیکی فیزیکی | صرف زمان برای راه رفتن یا دویدن | فضای باز، در معرض تمام شرایط آب و هوایی | هماهنگ‌کردن یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض آلاینده‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | فشار زمانی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارکنان | محیط داخلی، بدون کنترل شرایط محیطی | نزدیکی فیزیکی | صرف زمان برای راه رفتن یا دویدن | فضای باز، در معرض تمام شرایط آب و هوایی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورهای کارخانه و سیستم‌های شیمیایی | تمیزکنندگان وسایل نقلیه و تجهیزات | کارگران ساختمانی | تکنولوژیست‌ها و تکنسین‌های مهندسی محیط زیست | مهندسان محیط زیست | تکنسین‌های علوم و حفاظت محیط زیست، از جمله بهداشت | کارگران مواد منفجره، متخصصان جابجایی مهمات و انفجارکاران | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | دستیاران--کارگران استخراج | کارگران نگهداری بزرگراه‌ها | کارگران عایق‌کاری، کف، سقف و دیوار | کارگران تعمیر و نگهداری، عمومی | تکنسین‌های پایش هسته‌ای | متخصصان بهداشت و ایمنی حرفه‌ای | اپراتورهای ماشین‌آلات مهندسی و سایر تجهیزات ساختمانی | هماهنگ‌کنندگان بازیافت | کارگران بازیافت و احیاء | جمع‌آوران زباله و مواد بازیافتی | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | اپراتورهای کارخانه و سیستم‌های تصفیه آب و فاضلاب</t>
+          <t>اپراتورهای کارخانه و سامانه‌های شیمیایی | تمیزکنندگان وسایل نقلیه و تجهیزات | کارگران ساختمانی | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | دستیاران--کارگران استخراج | کارگران نگهداری بزرگراه‌ها | کارگران عایق‌کاری کف، سقف و دیوار | کارگران نگهداری و تعمیرات عمومی | تکنسین‌های نظارت هسته‌ای | متخصصان بهداشت و ایمنی شغلی | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | هماهنگ‌کنندگان بازیافت | کارگران بازیافت و احیا | جمع‌آوران زباله و مواد بازیافتی | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Database software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار پایگاه داده | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>پایش | سخن‌گفتن | گوش‌دادن فعال</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | زبان انگلیسی | ترابری | ساختمان و ساخت‌وساز | آموزش و پرورش | مدیریت و اداره امور</t>
+          <t>ایمنی و امنیت عمومی | زبان انگلیسی | حمل و نقل | ساختمان و ساخت‌وساز | آموزش و پرورش | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چند عضو | ثبات بازو-دست | حساسیت به مسئله | درک شفاهی | قدرت ایستا | بینایی نزدیک | توجه شنیداری | زبردستی دستی | ترتیب‌دهی به اطلاعات | بیان شفاهی | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | بینایی دور | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت تنه | زمان عکس‌العمل | جهت‌گیری پاسخ | زبردستی انگشتان | وضوح گفتار | تشخیص گفتار | درک عمق | کنترل سرعت | اشتراک زمانی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
+          <t>دقت کنترل | هماهنگی چند عضو | ثبات دست و بازو | حساسیت به مسئله | درک شفاهی | قدرت ایستا | بینایی نزدیک | توجه شنیداری | مهارت دستی | ترتیب‌دهی اطلاعات | بیان شفاهی | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | بینایی دور | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت تنه | زمان عکس‌العمل | جهت‌گیری پاسخ | مهارت انگشتان | وضوح گفتار | تشخیص گفتار | درک عمق | کنترل نرخ | تقسیم توجه | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض تمام شرایط آب و هوایی | پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | در معرض آلاینده‌ها بودن | کار با یا مشارکت در یک گروه کاری یا تیم | در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | در معرض تجهیزات خطرناک بودن | ارتباط با دیگران | در معرض دمای بسیار گرم یا سرد بودن | فراوانی تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | پیامد خطا | صرف زمان برای خم شدن یا چرخاندن بدن | اهمیت دقیق یا درست بودن | در معرض ارتعاش کل بدن بودن | بهداشت و ایمنی سایر کارگران | صرف زمان به صورت ایستاده | پیامدهای کاری و نتایج سایر کارگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سروکار داشتن با مشتریان خارجی یا عموم مردم | نزدیکی فیزیکی | فشار زمانی | موقعیت‌های تعارض | در یک وسیله نقلیه روباز یا کار با تجهیزات روباز | در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها بودن | در معرض شرایط نوری بسیار روشن یا ناکافی | فضای بسته، بدون دمای کنترل‌شده | مکالمات تلفنی | هماهنگ‌کردن یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف مشابه</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض تجهیزات خطرناک | ارتباط با دیگران | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فراوانی تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | پیامد خطا | صرف زمان برای خم کردن یا چرخاندن بدن | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض ارتعاش کل بدن | سلامت و ایمنی سایر کارکنان | صرف زمان برای ایستادن | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | نزدیکی فیزیکی | فشار زمانی | موقعیت‌های تعارض | در یک وسیله نقلیه روباز یا کار با تجهیزات | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | محیط داخلی، بدون کنترل شرایط محیطی | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | کارگران ساختمانی | نصابان و تعمیرکاران خطوط انتقال نیروی برق | اپراتورهای ماشین‌آلات خاک‌برداری، بارگیری و دراگ‌لاین، معدن‌کاری سطحی | کارگران حذف مواد خطرناک | رانندگان کامیون‌های سنگین و تریلی | دستیاران--برق‌کاران | دستیاران--کارگران استخراج | اپراتورهای کامیون و تراکتور صنعتی | اپراتورهای ماشین‌آلات بارگیری و جابجایی، معدن‌کاری زیرزمینی | کارگران تعمیر و نگهداری، عمومی | اپراتورهای ماشین‌آلات مهندسی و سایر تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، آسفالت و کوبیدن | اپراتورهای شمع‌کوب | تعمیرکاران واگن‌های ریلی | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | تکنسین‌های ترافیک | مهندسان حمل و نقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل و نقل، به جز هوانوردی</t>
+          <t>مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | کارگران ساختمانی | نصابان و تعمیرکاران خطوط انتقال نیروی برق | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | کارگران حذف مواد خطرناک | رانندگان کامیون‌های سنگین و تریلی | دستیاران--برق‌کاران | دستیاران--کارگران استخراج | اپراتورهای تراکتور و کامیون صنعتی | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | کارگران نگهداری و تعمیرات عمومی | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | اپراتورهای کوبنده شمع | تعمیرکنندگان واگن‌های ریلی | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | تکنسین‌های ترافیک | مهندسان حمل و نقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | پایش | گوش‌دادن فعال</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ترابری | مکانیک | ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | مدیریت و اداره امور</t>
+          <t>حمل و نقل | مکانیک | ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دقت کنترل | زبردستی دستی | هماهنگی چند عضو | ثبات بازو-دست | زمان عکس‌العمل | بینایی دور | حساسیت به مسئله | انعطاف‌پذیری بستار | درک عمق | بینایی نزدیک | تجسم | سرعت ادراکی | کنترل سرعت | قدرت ایستا | درک شفاهی | توجه شنیداری | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت پویا | جهت‌گیری پاسخ | زبردستی انگشتان | توجه انتخابی | ترتیب‌دهی به اطلاعات | استدلال قیاسی | حساسیت شنوایی | هماهنگی کلی بدن | استقامت | استدلال استقرایی | بیان شفاهی</t>
+          <t>دقت کنترل | مهارت دستی | هماهنگی چند عضو | ثبات دست و بازو | زمان عکس‌العمل | بینایی دور | حساسیت به مسئله | انعطاف‌پذیری بستار | درک عمق | بینایی نزدیک | تجسم | سرعت ادراکی | کنترل نرخ | قدرت ایستا | درک شفاهی | توجه شنیداری | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت پویا | جهت‌گیری پاسخ | مهارت انگشتان | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت شنوایی | هماهنگی کلی بدن | استقامت | استدلال استقرایی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده بودن | ارتباط با دیگران | مکالمات تلفنی | نزدیکی فیزیکی | بهداشت و ایمنی سایر کارگران | در معرض دمای بسیار گرم یا سرد بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | در معرض تجهیزات خطرناک بودن | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | تعیین وظایف، اولویت‌ها و اهداف | هماهنگ‌کردن یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارگران | آزادی در تصمیم‌گیری | در معرض آلاینده‌ها بودن | در معرض شرایط نوری بسیار روشن یا ناکافی | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | فشار زمانی | در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها بودن | پیامد خطا | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان به صورت ایستاده | صرف زمان برای خم شدن یا چرخاندن بدن | در معرض ارتعاش کل بدن بودن | سرعت تعیین‌شده توسط سرعت تجهیزات | فراوانی تصمیم‌گیری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | ارتباط با دیگران | مکالمات تلفنی | نزدیکی فیزیکی | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض تجهیزات خطرناک | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | فشار زمانی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای ایستادن | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض ارتعاش کل بدن | سرعت تعیین‌شده توسط سرعت تجهیزات | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان ساختار، سطوح، تجهیزات و سیستم‌های هواپیما | کارگران ساختمانی | اپراتورهای ماشین‌آلات استخراج مداوم | حفاران زمین، به جز نفت و گاز | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | اپراتورهای ماشین‌آلات خاک‌برداری، بارگیری و دراگ‌لاین، معدن‌کاری سطحی | کارگران نگهداری بزرگراه‌ها | اپراتورهای بالابر و وینچ | اپراتورهای ماشین‌آلات بارگیری و جابجایی، معدن‌کاری زیرزمینی | سازندگان آسیاب و نصابان ماشین‌آلات صنعتی (Millwrights) | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | اپراتورهای ماشین‌آلات مهندسی و سایر تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، آسفالت و کوبیدن | اپراتورهای شمع‌کوب | لوله‌گذاران | تعمیرکاران واگن‌های ریلی | ریگرها (دکل‌بندها) | اپراتورهای مته چرخشی، نفت و گاز | کارگران ساده (Roustabouts)، نفت و گاز | کارگران آهن و فولاد ساختمانی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | کارگران ساختمانی | اپراتورهای ماشین استخراج مداوم | حفاران زمین، به جز نفت و گاز | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | کارگران نگهداری بزرگراه‌ها | اپراتورهای بالابر و وینچ | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | اپراتورهای کوبنده شمع | لوله‌گذاران | تعمیرکنندگان واگن‌های ریلی | ریگرها | اپراتورهای مته چرخشی، نفت و گاز | کارگران فنی همه‌کاره نفت و گاز | کارگران سازه‌های آهنی و فولادی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Intuit QuickBooks | Microsoft Excel | Microsoft Word | Route mapping software | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار</t>
+          <t>Intuit QuickBooks | Microsoft Excel | Microsoft Word | نرم‌افزار نقشه‌برداری مسیر | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش‌دادن فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | ترابری | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | مدیریت و اداره امور</t>
+          <t>خدمات مشتری و شخصی | حمل و نقل | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>زبردستی دستی | دقت کنترل | هماهنگی چند عضو | ثبات بازو-دست | انعطاف‌پذیری بستار | حساسیت به مسئله | درک شفاهی | درک عمق | زمان عکس‌العمل | بینایی نزدیک | حساسیت شنوایی | استدلال قیاسی | بیان شفاهی | بینایی دور | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | توجه شنیداری | قدرت تنه | توجه انتخابی | تجسم | سرعت ادراکی | استدلال استقرایی</t>
+          <t>مهارت دستی | دقت کنترل | هماهنگی چند عضو | ثبات دست و بازو | انعطاف‌پذیری بستار | حساسیت به مسئله | درک شفاهی | درک عمق | زمان عکس‌العمل | بینایی نزدیک | حساسیت شنوایی | استدلال قیاسی | بیان شفاهی | بینایی دور | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | توجه شنیداری | قدرت تنه | توجه انتخابی | تجسم | سرعت ادراکی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>فضای باز, در معرض تمام شرایط آب و هوایی | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | در معرض آلاینده‌ها بودن | پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | سروکار داشتن با مشتریان خارجی یا عموم مردم | در معرض دمای بسیار گرم یا سرد بودن | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده بودن | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | در معرض شرایط نوری بسیار روشن یا ناکافی | هماهنگ‌کردن یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | بهداشت و ایمنی سایر کارگران | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | در معرض تجهیزات خطرناک بودن | پیامدهای کاری و نتایج سایر کارگران | صرف زمان برای خم شدن یا چرخاندن بدن | در یک وسیله نقلیه روباز یا کار با تجهیزات روباز | در معرض بیماری یا عفونت‌ها بودن | صرف زمان برای انجام حرکات تکراری</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض تجهیزات خطرناک | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای خم کردن یا چرخاندن بدن | در یک وسیله نقلیه روباز یا کار با تجهیزات | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تمیزکنندگان وسایل نقلیه و تجهیزات | کارگران ساختمانی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌آلات خاک‌برداری، بارگیری و دراگ‌لاین، معدن‌کاری سطحی | کارگران حذف مواد خطرناک | دستیاران--کارگران استخراج | دستیاران--لوله‌گذاران، لوله‌کشان، لوله‌کشان صنعتی و لوله‌کشان بخار | کارگران نگهداری بزرگراه‌ها | کارگران تعمیر و نگهداری، عمومی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | اپراتورهای ماشین‌آلات مهندسی و سایر تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، آسفالت و کوبیدن | لوله‌گذاران | لوله‌کشان، لوله‌کشان صنعتی و لوله‌کشان بخار | اپراتورهای پمپ، به جز پمپ‌های سرچاهی | اپراتورهای مته چرخشی، نفت و گاز | کارگران ساده (Roustabouts)، نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | اپراتورهای کارخانه و سیستم‌های تصفیه آب و فاضلاب</t>
+          <t>تمیزکنندگان وسایل نقلیه و تجهیزات | کارگران ساختمانی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | کارگران حذف مواد خطرناک | دستیاران--کارگران استخراج | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران نگهداری بزرگراه‌ها | کارگران نگهداری و تعمیرات عمومی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | لوله‌گذاران | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | اپراتورهای مته چرخشی، نفت و گاز | کارگران فنی همه‌کاره نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Database software | Decorative Software Online Visualizers | Depiction Software Deco-Con | Depiction Software Deco-Con Estimator | Depiction Software Hardscape Imaging | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | UNI-GROUP Lockpave Pro | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار پایگاه داده | Decorative Software Online Visualizers | Depiction Software Deco-Con | Depiction Software Deco-Con Estimator | Depiction Software Hardscape Imaging | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | UNI-GROUP Lockpave Pro | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | سخن‌گفتن | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>هماهنگی چند عضو | درک شفاهی | بیان شفاهی | دقت کنترل | بینایی نزدیک | زبردستی دستی | ثبات بازو-دست | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی به اطلاعات | قدرت ایستا | زبردستی انگشتان | استدلال استقرایی | استدلال قیاسی | درک عمق | قدرت تنه | زمان عکس‌العمل | تجسم | انعطاف‌پذیری دسته‌بندی | بیان کتبی | درک کتبی</t>
+          <t>هماهنگی چند عضو | درک شفاهی | بیان شفاهی | دقت کنترل | بینایی نزدیک | مهارت دستی | ثبات دست و بازو | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | قدرت ایستا | مهارت انگشتان | استدلال استقرایی | استدلال قیاسی | درک عمق | قدرت تنه | زمان عکس‌العمل | تجسم | انعطاف‌پذیری دسته‌بندی | بیان کتبی | درک کتبی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | سروکار داشتن با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | فضای باز، در معرض تمام شرایط آب و هوایی | هماهنگ‌کردن یا هدایت دیگران در انجام فعالیت‌های کاری | پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده بودن | آزادی در تصمیم‌گیری | فشار زمانی | پیامدهای کاری و نتایج سایر کارگران | فراوانی تصمیم‌گیری | موقعیت‌های تعارض | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | در معرض دمای بسیار گرم یا سرد بودن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | نزدیکی فیزیکی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فضای باز، در معرض تمام شرایط آب و هوایی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | آزادی در تصمیم‌گیری | فشار زمانی | پیامدهای کاری و نتایج سایر کارکنان | فراوانی تصمیم‌گیری | موقعیت‌های تعارض | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>بناهای آجر و بلوک | نجاران | نصابان فرش | بناهای سیمان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | لایه‌گذاران کف، به جز فرش، چوب و تایل‌های سخت | سنباده‌زنان و پرداخت‌کاران کف | دستیاران--بناهای آجر، بلوک، سنگ، و نصابان تایل و مرمر | دستیاران--سقف‌کاران | کارگران عایق‌کاری، کف، سقف و دیوار | اپراتورهای تجهیزات روسازی، آسفالت و کوبیدن | گچ‌کاران و بناهای سیمان‌کاری تزئینی (استاکو) | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | برش‌دهندگان سنگ، معدن | سقف‌کاران | برش‌دهندگان و تراش‌دهندگان سنگ، تولیدی | بناهای سنگ‌کار | کارگران و پرداخت‌کاران موزاییک درجا (ترازو) | نصابان تایل و سنگ</t>
+          <t>بنّایان آجرکار و بلوک‌کار | نجّاران | نصّابان موکت و فرش | بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | سنباده‌کاران و پرداخت‌کاران کف | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--سقف‌سازان | کارگران عایق‌کاری کف، سقف و دیوار | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | گچ‌کاران و بناهای سیمان‌کاری | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | سنگ‌شکنان معدن | سقف‌سازان | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | بنّایان سنگ‌کار | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | Database software | نرم‌افزار زمان‌بندی | Microsoft Outlook | Inventory management systems | نرم‌افزار Microsoft Office | Computerized maintenance management system CMMS</t>
+          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>پایش | گوش‌دادن فعال | تفکر انتقادی | درک مطلب | سخن‌گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>زبردستی دستی | زبردستی انگشتان | ثبات بازو-دست | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض دمای بسیار گرم یا سرد بودن | در معرض آلاینده‌ها بودن | در معرض تجهیزات خطرناک بودن | در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده بودن | پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم شدن یا چرخاندن بدن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | در معرض ارتفاعات بالا بودن | بهداشت و ایمنی سایر کارگران | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | پیامد خطا | صرف زمان برای راه رفتن یا دویدن | در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها بودن</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض ارتفاعات بالا | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | پیامد خطا | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارگران ساختمانی | نجاران | بناهای سیمان و پرداخت‌کاران بتن | بناهای آجر و بلوک | بناهای سنگ‌کار | سنگ‌فرش‌کاران قطعه‌ای | نصابان حصار | کارگران حذف مواد خطرناک | کارگران نگهداری بزرگراه‌ها | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | بازرسان ساخت‌وساز و ساختمان | نصابان و تکنسین‌های عایق‌سازی و مقاوم‌سازی در برابر شرایط جوی | کارگران عایق‌کاری، کف، سقف و دیوار | اپراتورهای ماشین‌آلات مهندسی و سایر تجهیزات ساختمانی | کارگران آهن و فولاد ساختمانی | سقف‌کاران | شیشه‌بران | نصابان ساختمان‌های پیش‌ساخته و خانه‌های متحرک | سرپرستان رده اول مشاغل ساختمانی و کارگران استخراج | دستیاران، مشاغل ساختمانی، سایر موارد</t>
+          <t>کارگران ساختمانی | نجّاران | بنّایان سیمان‌کار و پرداخت‌کاران بتن | بنّایان آجرکار و بلوک‌کار | بنّایان سنگ‌کار | سنگ‌فرش‌کاران قطعه‌ای | نصابان حصار | کارگران حذف مواد خطرناک | کارگران نگهداری بزرگراه‌ها | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | بازرسان ساختمان و ساخت‌وساز | نصابان و تکنسین‌های عایق‌سازی و مقاوم‌سازی در برابر شرایط جوی | کارگران عایق‌کاری کف، سقف و دیوار | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | کارگران سازه‌های آهنی و فولادی | سقف‌سازان | شیشه‌بران | نصاب ساختمان‌های پیش‌ساخته و خانه‌های سیار | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | دستیاران، مشاغل ساختمانی، سایر</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Database software | Energy auditing software | Energy use ratings databases | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word | نرم‌افزار SAP | Salesforce.com Salesforce CRM | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار</t>
+          <t>نرم‌افزار پایگاه داده | Energy auditing software | Energy use ratings databases | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word | نرم‌افزار SAP | Salesforce.com Salesforce CRM | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>پایش | تفکر انتقادی | گوش‌دادن فعال | سخن‌گفتن | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | خدمات مشتریان و شخصی | مکانیک | مدیریت و اداره امور | آموزش و پرورش | ریاضیات | زبان انگلیسی | ایمنی و امنیت عمومی | اداری | کامپیوتر و الکترونیک | اقتصاد و حسابداری | تولید و فرآوری | طراحی</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مکانیک | مدیریت و اداره | آموزش و پرورش | ریاضیات | زبان انگلیسی | ایمنی و امنیت عمومی | اداری | رایانه و الکترونیک | اقتصاد و حسابداری | تولید و فرآوری | طراحی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | حساسیت به مسئله | زبردستی دستی | درک شفاهی | بیان شفاهی | ترتیب‌دهی به اطلاعات | ثبات بازو-دست | هماهنگی چند عضو | تجسم | انعطاف‌پذیری بستار | درک عمق | بینایی دور | انعطاف‌پذیری دامنه حرکت | قدرت تنه | وضوح گفتار | تشخیص گفتار | تشخیص بصری رنگ | زمان عکس‌العمل | دقت کنترل | زبردستی انگشتان | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | روان بودن ایده‌ها</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | مهارت دستی | درک شفاهی | بیان شفاهی | ترتیب‌دهی اطلاعات | ثبات دست و بازو | هماهنگی چند عضو | تجسم | انعطاف‌پذیری بستار | درک عمق | بینایی دور | انعطاف‌پذیری دامنه حرکت | قدرت تنه | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | زمان عکس‌العمل | دقت کنترل | مهارت انگشتان | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | پوشیدن تجهیزات محافظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | فضای باز، در معرض تمام شرایط آب و هوایی | بهداشت و ایمنی سایر کارگران | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | پوشیدن تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | در معرض فضای کاری تنگ، موقعیت‌های نامناسب بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده | در معرض تجهیزات خطرناک بودن | فشار زمانی | پیامدهای کاری و نتایج سایر کارگران | هماهنگ‌کردن یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | سروکار داشتن با مشتریان خارجی یا عموم مردم | در معرض دمای بسیار گرم یا سرد بودن | در معرض آلاینده‌ها بودن | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | فضای بسته، با دمای کنترل‌شده | اهمیت دقیق یا درست بودن | فضای بسته، بدون دمای کنترل‌شده</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | فضای باز، در معرض تمام شرایط آب و هوایی | سلامت و ایمنی سایر کارکنان | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | قرار گرفتن در معرض تجهیزات خطرناک | فشار زمانی | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | محیط داخلی، بدون کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>دیگ‌سازان | مدیران ساخت‌وساز | بازرسان ساخت‌وساز و ساختمان | بازرسان انرژی | مهندسان انرژی، به جز باد و خورشید | تکنسین‌های زمین‌گرمایی | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | دستیاران--کارگران نصب، تعمیر و نگهداری | دستیاران--لوله‌گذاران، لوله‌کشان، لوله‌کشان صنعتی و لوله‌کشان بخار | کارگران عایق‌کاری، کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | کارگران تعمیر و نگهداری، عمومی | لوله‌کشان، لوله‌کشان صنعتی و لوله‌کشان بخار | سقف‌کاران | کارگران ورق‌کار فلزی | مدیران نصب انرژی خورشیدی | نصابان خورشیدی فتوولتائیک | نصابان و تکنسین‌های حرارتی خورشیدی | مهندسان تاسیسات و اپراتورهای دیگ بخار | تکنسین‌های خدمات توربین بادی</t>
+          <t>دیگ‌سازان | مدیران ساخت‌وساز | بازرسان ساختمان و ساخت‌وساز | بازرسان انرژی | مهندسان انرژی، به جز باد و خورشید | تکنسین‌های زمین‌گرمایی | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | کارگران نگهداری و تعمیرات عمومی | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | سقف‌سازان | کارگران ورق‌کاری | مدیران نصب انرژی خورشیدی | نصابان سیستم‌های فتوولتائیک خورشیدی | نصابان و تکنسین‌های حرارتی خورشیدی | مهندسان تاسیسات و اپراتورهای دیگ بخار | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0076_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0076_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | شنیدن فعال | تفکر انتقادی | نگارش | ریاضیات | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | ریاضیات | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ساختمان‌سازی و سازه | ریاضیات | مهندسی و فناوری | مکانیک | فیزیک | زبان انگلیسی | فروش و بازاریابی | طراحی | رایانه و الکترونیک | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | ریاضیات | مهندسی و فناوری | مکانیک | فیزیک | زبان انگلیسی | فروش و بازاریابی | طراحی | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | استدلال ریاضی | دید نزدیک | محاسبات عددی | مرتب‌سازی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری بستار | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری طبقه‌بندی | تجسم فضایی | سرعت ادراک | سرعت بستار | ابتکار و اصالت | دید دور | دقت کنترل</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | استدلال ریاضی | بینایی نزدیک | توانایی عددی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری بستار | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | تجسم | سرعت ادراکی | سرعت بستار | اصالت | بینایی دور | دقت کنترل</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | مدیران نیروگاه‌های زیست‌توده | بازرسان ساختمان و ابنیه | مهندسان انرژی، به‌جز باد و خورشید | کارشناسان و تکنسین‌های مهندسی محیط زیست | مدیران تولید انرژی زمین‌گرمایی | بوم‌شناسان صنعتی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | توزیع‌کنندگان و دیسپچرهای برق | مدیران نصب سیستم‌های خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های فتوولتائیک خورشیدی | کارشناسان فروش و ارزیابان انرژی خورشیدی | متخصصان پایداری و تاب‌آوری زیست‌محیطی | مهندسان آب و فاضلاب | نصابان و تکنسین‌های عایق‌کاری و بهسازی مصرف انرژی | مدیران توسعه انرژی بادی | مهندسان انرژی بادی | تکنسین‌های نگهداری و تعمیرات توربین بادی</t>
+          <t>مدیران توسعه محصول و فناوری زیست‌سوخت | مدیران نیروگاه‌های زیست‌توده | بازرسان ساخت‌وساز و ساختمان | مهندسان انرژی، به‌جز بادی و خورشیدی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مدیران تولید انرژی زمین‌گرمایی | بوم‌شناسان صنعتی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | دیسپچرها و توزیع‌کنندگان شبکه برق | مدیران اجرای پروژه‌های انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های خورشیدی فتوولتائیک | کارشناسان فروش و ارزیابان سامانه‌های خورشیدی | کارشناسان پایداری و توسعه پایدار | مهندسان آب و فاضلاب | نصابان و تکنسین‌های عایق‌کاری و بهسازی مصرف انرژی | مدیران توسعه پروژه‌های انرژی بادی | مهندسان انرژی باد | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | یادگیری فعال | نظارت | سخن گفتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | ساختمان‌سازی و سازه | ایمنی و امنیت عمومی | رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | مدیریت و امور اداری</t>
+          <t>مکانیک | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | حساسیت به مسئله | چابکی دستی | درک شفاهی | دید نزدیک | چابکی انگشتان | پایداری دست و بازو | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری دامنه حرکتی | تجسم فضایی | دقت کنترل | بیان شفاهی | بیان کتبی | درک کتبی | تعادل عمومی بدن | قدرت تنه | زمان واکنش | هماهنگی چند عضو | انعطاف‌پذیری بستار | انعطاف‌پذیری طبقه‌بندی | تشخیص گفتار | توجه انتخابی</t>
+          <t>استدلال قیاسی | حساسیت به مسئله | مهارت دستی | درک شفاهی | بینایی نزدیک | مهارت انگشتان | ثبات دست و بازو | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دامنه حرکت | تجسم | دقت کنترل | بیان شفاهی | بیان کتبی | درک کتبی | تعادل کلی بدن | قدرت تنه | زمان عکس‌العمل | هماهنگی چند عضو | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان صنعتی | مکانیک‌های اتوبوس، کامیون و متخصصان موتور دیزل | نصابان و تعمیرکاران شیرآلات و سیستم‌های کنترلی، به‌جز درهای مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات مرتبط | نصابان و تعمیرکاران خطوط انتقال نیرو | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | مونتاژکاران موتور و سایر ماشین‌آلات صنعتی | مکانیک‌ها و نصابان سیستم‌های سرمایش، گرمایش و تهویه مطبوع | کارگران کمکی نصابان و تعمیرکاران | اپراتورهای وینچ و بالابر صنعتی | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری و تعمیرات عمومی | تعمیرکاران درهای مکانیکی و برقی | تکنسین‌های نصب و راه‌اندازی ماشین‌آلات صنعتی (میلرایت) | مکانیک‌های ماشین‌آلات سنگین متحرک، به‌جز موتور | لوله‌کش‌ها و تأسیسات‌کاران خطوط بخار و پایپینگ | تعمیرکاران واگن‌های ریلی | ریگرها و قلاب‌اندازان | کارگران سازه‌های فلزی و اسکلت فولادی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | کارگران کمکی نصب، نگهداری و تعمیرات | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | کارگران عمومی تعمیرات و نگهداری تاسیسات | تعمیرکاران درب‌های مکانیکی و اتوماتیک | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | تعمیرکار واگن قطار | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | اسکلت‌سازان و نصابان سازه‌های فولادی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>فنس‌ساز | پیمانکار فنس و حصارکشی | حصاربند | نصاب فنس | کارگر فنس‌کشی | مکانیک حصار | تکنسین فنس و حصار | تکنسین درهای اتوماتیک و حفاظ | نصاب حصارهای چوبی</t>
+          <t>سازنده حصار | پیمانکار حصار | نصاب حصار | نصب‌کننده حصار | کارگر حصار | مکانیک حصار | تکنسین حصار (Fence Tech) | تکنسین دروازه (Gate Tech) | نصاب حصار چوبی</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ساختمان‌سازی و سازه | حمل‌ونقل | مدیریت و امور اداری | طراحی | ریاضیات | زبان انگلیسی | آموزش و تدریس | مکانیک | فروش و بازاریابی | تولید و فرآوری | مهندسی و فناوری | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | حمل و نقل | مدیریت و اداره | طراحی | ریاضیات | زبان انگلیسی | آموزش و پرورش | مکانیک | فروش و بازاریابی | تولید و فرآوری | مهندسی و فناوری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>قدرت تنه | چابکی دستی | هماهنگی چند عضو | قدرت ایستا | پایداری دست و بازو | چابکی انگشتان | دقت کنترل | مرتب‌سازی اطلاعات | دید نزدیک | استقامت جسمانی | قدرت پویا | تشخیص گفتار | ادراک عمق | انعطاف‌پذیری دامنه حرکتی | زمان واکنش | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
+          <t>قدرت تنه | مهارت دستی | هماهنگی چند عضو | قدرت ایستا | ثبات دست و بازو | مهارت انگشتان | دقت کنترل | ترتیب‌دهی اطلاعات | بینایی نزدیک | استقامت | قدرت پویا | تشخیص گفتار | درک عمق | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>نجاران | سیمان‌کاران و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان صفحات گچی (درای‌وال) و تایل‌های سقف کاذب | نصابان و تعمیرکاران خطوط انتقال نیرو | برق‌کاران | کارگران کمکی نجاران | کارگران کمکی برق‌کاران | کارگران کمکی لوله‌کشان و تأسیسات‌کاران | عایق‌کاران کف، سقف و دیوار ساختمان | عایق‌کاران تأسیسات مکانیکی | خط‌کشان و برش‌کاران قطعات فلزی و پلاستیکی | تعمیرکاران درهای مکانیکی و برقی | لوله‌گذاران خطوط لوله | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | آرماتوربندان و بتن‌ریزان | سقف‌کاران و عایق‌کاران پشت‌بام | سازندگان و ورق‌کاران فلزی | کارگران سازه‌های فلزی و اسکلت فولادی | مونتاژکاران و نصابان سازه‌های فلزی</t>
+          <t>نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | برق‌کاران | کمک‌نجاران | کمک‌برق‌کاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تعمیرکاران درب‌های مکانیکی و اتوماتیک | لوله‌گذاران خطوط انتقال | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | آرماتوربندان و نصابان میلگرد | عایق‌کاران و نصابان پوشش‌های سقفی | کارگران ورق‌کاری فلزی | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | یادگیری فعال | نگارش</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مدیریت و امور اداری | حمل‌ونقل | خدمات مشتریان و خدمات فردی | ساختمان‌سازی و سازه | مکانیک | زبان انگلیسی</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره | حمل و نقل | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | مکانیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | دقت کنترل | دید نزدیک | بیان شفاهی | تشخیص گفتار | پایداری دست و بازو | انعطاف‌پذیری طبقه‌بندی | استدلال قیاسی | بیان کتبی | هماهنگی چند عضو | مرتب‌سازی اطلاعات | استدلال استقرایی | تجسم فضایی | چابکی دستی | وضوح گفتار | درک کتبی | انعطاف‌پذیری دامنه حرکتی | توجه انتخابی | دید دور | قدرت ایستا | چابکی انگشتان | سرعت ادراک | انعطاف‌پذیری بستار</t>
+          <t>حساسیت به مسئله | درک شفاهی | دقت کنترل | بینایی نزدیک | بیان شفاهی | تشخیص گفتار | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان کتبی | هماهنگی چند عضو | ترتیب‌دهی اطلاعات | استدلال استقرایی | تجسم | مهارت دستی | وضوح گفتار | درک کتبی | انعطاف‌پذیری دامنه حرکت | توجه انتخابی | بینایی دور | قدرت ایستا | مهارت انگشتان | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورهای کارخانجات و سیستم‌های صنایع شیمیایی | پاک‌کنندگان و شست‌وشوکاران وسایل نقلیه و تجهیزات | کارگران ساختمانی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط زیست | تکنسین‌های بهداشت و علوم حفاظت از محیط زیست | کارگران مواد ناریه، کارشناسان جابه‌جایی مهمات و آتش‌بارها | مهندسان بهداشت و ایمنی حرفه‌ای، به‌جز ایمنی معدن | کارگران کمکی استخراج معدن | کارگران نگهداری و راهداری بزرگراه‌ها | عایق‌کاران کف، سقف و دیوار ساختمان | کارگران نگهداری و تعمیرات عمومی | تکنسین‌های پایش و حفاظت پرتوی هسته‌ای | کارشناسان بهداشت حرفه‌ای و طب کار | اپراتورهای ماشین‌آلات سنگین ساختمانی و مهندسی | هماهنگ‌کنندگان بازیافت | کارگران بازیافت و بازیافت مواد | جمع‌آوری‌کنندگان زباله و مواد بازیافتی | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | اپراتورهای تصفیه‌خانه و شبکه‌های توزیع آب و فاضلاب</t>
+          <t>اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | کارگران ساختمانی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان مواد منفجره و آتش‌باری | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | کارگران کمکی استخراج معدن | کارگران راهداری و نگهداری جاده‌ها | عایق‌کاران کف، سقف و دیوار | کارگران عمومی تعمیرات و نگهداری تاسیسات | تکنسین‌های پایش و حفاظت پرتوی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | هماهنگ‌کنندگان امور بازیافت | کارگران بازیافت و تفکیک پسماند | متصدیان و رانندگان جمع‌آوری پسماند و مواد بازیافتی | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,22 +731,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار پایگاه داده | نرم‌افزار مرورگر وب | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word</t>
+          <t>نرم‌افزار پایگاه داده | نرم‌افزار مرورگر وب | نرم‌افزار Microsoft Office | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | زبان انگلیسی | حمل‌ونقل | ساختمان‌سازی و سازه | آموزش و تدریس | مدیریت و امور اداری</t>
+          <t>ایمنی و امنیت عمومی | زبان انگلیسی | حمل و نقل | ساختمان و ساخت‌وساز | آموزش و پرورش | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چند عضو | پایداری دست و بازو | حساسیت به مسئله | درک شفاهی | قدرت ایستا | دید نزدیک | توجه شنوایی | چابکی دستی | مرتب‌سازی اطلاعات | بیان شفاهی | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری بستار | دید دور | انعطاف‌پذیری دامنه حرکتی | استقامت جسمانی | قدرت تنه | زمان واکنش | جهت‌گیری پاسخ | چابکی انگشتان | وضوح گفتار | تشخیص گفتار | ادراک عمق | کنترل نرخ پیشروی | اشتراک زمانی | سرعت ادراک | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | استدلال قیاسی</t>
+          <t>دقت کنترل | هماهنگی چند عضو | ثبات دست و بازو | حساسیت به مسئله | درک شفاهی | قدرت ایستا | بینایی نزدیک | توجه شنیداری | مهارت دستی | ترتیب‌دهی اطلاعات | بیان شفاهی | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | بینایی دور | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت تنه | زمان عکس‌العمل | جهت‌گیری پاسخ | مهارت انگشتان | وضوح گفتار | تشخیص گفتار | درک عمق | کنترل نرخ | تقسیم توجه | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مکانیک‌های اتوبوس، کامیون و متخصصان موتور دیزل | کارگران ساختمانی | نصابان و تعمیرکاران خطوط انتقال نیرو | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن سطحی | کارگران امحا و پاک‌سازی مواد خطرناک | رانندگان کامیون‌های سنگین و تریلر | کارگران کمکی برق‌کاران | کارگران کمکی استخراج معدن | اپراتورهای لیفتراک و تراکتورهای صنعتی | اپراتورهای ماشین‌آلات بارگیری و باربری در معادن زیرزمینی | کارگران نگهداری و تعمیرات عمومی | اپراتورهای ماشین‌آلات سنگین ساختمانی و مهندسی | اپراتورهای ماشین‌آلات آسفالت‌کاری، تسطیح و تراکم‌کوبی | اپراتورهای ماشین‌آلات شمع‌کوبی | تعمیرکاران واگن‌های ریلی | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | تکنسین‌های مهندسی ترافیک | مهندسان حمل‌ونقل و ترابری | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های ترابری، به‌جز هوانوردی</t>
+          <t>مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | کارگران ساختمانی | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | کارگران امحا و پاک‌سازی مواد خطرناک | رانندگان خودروهای سنگین و کشنده‌ها | کمک‌برق‌کاران | کارگران کمکی استخراج معدن | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | کارگران عمومی تعمیرات و نگهداری تاسیسات | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | اپراتورهای دستگاه شمع‌کوب | تعمیرکار واگن قطار | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | تکنسین‌های ترافیک | مهندسان حمل‌ونقل و ترافیک | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,22 +788,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>نرم‌افزار ثبت ساعت کار و حضور و غیاب | Microsoft Excel | Microsoft Office software</t>
+          <t>نرم‌افزار ثبت ساعت کار و حضور و غیاب | نرم‌افزار Microsoft Office | نرم‌افزار ثبت زمان</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | مکانیک | ساختمان‌سازی و سازه | ایمنی و امنیت عمومی | مدیریت و امور اداری</t>
+          <t>حمل و نقل | مکانیک | ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دقت کنترل | چابکی دستی | هماهنگی چند عضو | پایداری دست و بازو | زمان واکنش | دید دور | حساسیت به مسئله | انعطاف‌پذیری بستار | ادراک عمق | دید نزدیک | تجسم فضایی | سرعت ادراک | کنترل نرخ پیشروی | قدرت ایستا | درک شفاهی | توجه شنوایی | انعطاف‌پذیری دامنه حرکتی | قدرت تنه | قدرت پویا | جهت‌گیری پاسخ | چابکی انگشتان | توجه انتخابی | مرتب‌سازی اطلاعات | استدلال قیاسی | حساسیت شنوایی | هماهنگی عمومی بدن | استقامت جسمانی | استدلال استقرایی | بیان شفاهی</t>
+          <t>دقت کنترل | مهارت دستی | هماهنگی چند عضو | ثبات دست و بازو | زمان عکس‌العمل | بینایی دور | حساسیت به مسئله | انعطاف‌پذیری بستار | درک عمق | بینایی نزدیک | تجسم | سرعت ادراکی | کنترل نرخ | قدرت ایستا | درک شفاهی | توجه شنیداری | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت پویا | جهت‌گیری پاسخ | مهارت انگشتان | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت شنوایی | هماهنگی کلی بدن | استقامت | استدلال استقرایی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | کارگران ساختمانی | اپراتورهای ماشین‌آلات استخراج پیوسته زغال‌سنگ | حفاران زمین، به‌جز نفت و گاز | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات مرتبط | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن سطحی | کارگران نگهداری و راهداری بزرگراه‌ها | اپراتورهای وینچ و بالابر صنعتی | اپراتورهای ماشین‌آلات بارگیری و باربری در معادن زیرزمینی | تکنسین‌های نصب و راه‌اندازی ماشین‌آلات صنعتی (میلرایت) | مکانیک‌های ماشین‌آلات سنگین متحرک، به‌جز موتور | اپراتورهای ماشین‌آلات سنگین ساختمانی و مهندسی | اپراتورهای ماشین‌آلات آسفالت‌کاری، تسطیح و تراکم‌کوبی | اپراتورهای ماشین‌آلات شمع‌کوبی | لوله‌گذاران خطوط لوله | تعمیرکاران واگن‌های ریلی | ریگرها و قلاب‌اندازان | حفاران دکل‌های چرخشی، نفت و گاز | کارگران ساده سکوی حفاری، نفت و گاز | کارگران سازه‌های فلزی و اسکلت فولادی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | کارگران ساختمانی | اپراتورهای ماشین‌های استخراج پیوسته | حفاران زمین، به‌جز نفت و گاز | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | کارگران راهداری و نگهداری جاده‌ها | اپراتورهای بالابر و وینچ | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | اپراتورهای دستگاه شمع‌کوب | لوله‌گذاران خطوط انتقال | تعمیرکار واگن قطار | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | حفاران دورانی نفت و گاز | کارگران عمومی سکو و میادین نفت و گاز | اسکلت‌سازان و نصابان سازه‌های فولادی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,22 +845,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>نرم‌افزار مسیریابی حمل‌ونقل | نرم‌افزار برنامه‌ریزی و زمان‌بندی کار | Intuit QuickBooks | Microsoft Excel | Microsoft Word | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار مسیریابی حمل‌ونقل | نرم‌افزار برنامه‌ریزی و زمان‌بندی کار | Intuit QuickBooks | نرم‌افزار نقشه‌برداری مسیر | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | حمل‌ونقل | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | حمل و نقل | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>چابکی دستی | دقت کنترل | هماهنگی چند عضو | پایداری دست و بازو | انعطاف‌پذیری بستار | حساسیت به مسئله | درک شفاهی | ادراک عمق | زمان واکنش | دید نزدیک | حساسیت شنوایی | استدلال قیاسی | بیان شفاهی | دید دور | انعطاف‌پذیری دامنه حرکتی | قدرت ایستا | توجه شنوایی | قدرت تنه | توجه انتخابی | تجسم فضایی | سرعت ادراک | استدلال استقرایی</t>
+          <t>مهارت دستی | دقت کنترل | هماهنگی چند عضو | ثبات دست و بازو | انعطاف‌پذیری بستار | حساسیت به مسئله | درک شفاهی | درک عمق | زمان عکس‌العمل | بینایی نزدیک | حساسیت شنوایی | استدلال قیاسی | بیان شفاهی | بینایی دور | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | توجه شنیداری | قدرت تنه | توجه انتخابی | تجسم | سرعت ادراکی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>پاک‌کنندگان و شست‌وشوکاران وسایل نقلیه و تجهیزات | کارگران ساختمانی | نصابان و تعمیرکاران شیرآلات و سیستم‌های کنترلی، به‌جز درهای مکانیکی | حفاران زمین، به‌جز نفت و گاز | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن سطحی | کارگران امحا و پاک‌سازی مواد خطرناک | کارگران کمکی استخراج معدن | کارگران کمکی لوله‌کشان و تأسیسات‌کاران | کارگران نگهداری و راهداری بزرگراه‌ها | کارگران نگهداری و تعمیرات عمومی | مکانیک‌های ماشین‌آلات سنگین متحرک، به‌جز موتور | اپراتورهای ماشین‌آلات سنگین ساختمانی و مهندسی | اپراتورهای ماشین‌آلات آسفالت‌کاری، تسطیح و تراکم‌کوبی | لوله‌گذاران خطوط لوله | لوله‌کش‌ها و تأسیسات‌کاران خطوط بخار و پایپینگ | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | حفاران دکل‌های چرخشی، نفت و گاز | کارگران ساده سکوی حفاری، نفت و گاز | اپراتورهای یونیت‌های خدمات فنی چاه، نفت و گاز | اپراتورهای تصفیه‌خانه و شبکه‌های توزیع آب و فاضلاب</t>
+          <t>شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | کارگران ساختمانی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | حفاران زمین، به‌جز نفت و گاز | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | کارگران امحا و پاک‌سازی مواد خطرناک | کارگران کمکی استخراج معدن | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | کارگران راهداری و نگهداری جاده‌ها | کارگران عمومی تعمیرات و نگهداری تاسیسات | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | لوله‌گذاران خطوط انتقال | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | حفاران دورانی نفت و گاز | کارگران عمومی سکو و میادین نفت و گاز | اپراتورهای واحدهای خدمات چاه نفت و گاز | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مکانیک | ساختمان‌سازی و سازه</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>هماهنگی چند عضو | درک شفاهی | بیان شفاهی | دقت کنترل | دید نزدیک | چابکی دستی | پایداری دست و بازو | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | قدرت ایستا | چابکی انگشتان | استدلال استقرایی | استدلال قیاسی | ادراک عمق | قدرت تنه | زمان واکنش | تجسم فضایی | انعطاف‌پذیری طبقه‌بندی | بیان کتبی | درک کتبی</t>
+          <t>هماهنگی چند عضو | درک شفاهی | بیان شفاهی | دقت کنترل | بینایی نزدیک | مهارت دستی | ثبات دست و بازو | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | قدرت ایستا | مهارت انگشتان | استدلال استقرایی | استدلال قیاسی | درک عمق | قدرت تنه | زمان عکس‌العمل | تجسم | انعطاف‌پذیری دسته‌بندی | بیان کتبی | درک کتبی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>بنایان و کارگران آجرچین و بلوک‌چین | نجاران | نصابان موکت و کف‌پوش‌های پرزدار | سیمان‌کاران و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان صفحات گچی (درای‌وال) و تایل‌های سقف کاذب | کف‌پوش‌کاران، به‌جز فرش، چوب و تایل‌های سخت | ساب‌زنان و صیقل‌کاران کف‌پوش چوبی | کارگران کمکی بنایان، سنگ‌کاران و کاشی‌کاران | کارگران کمکی سقف‌کاران | عایق‌کاران کف، سقف و دیوار ساختمان | اپراتورهای ماشین‌آلات آسفالت‌کاری، تسطیح و تراکم‌کوبی | گچ‌کاران و سفیدکاران | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | سنگ‌شکنان و کارگران استخراج سنگ از معدن | سقف‌کاران و عایق‌کاران پشت‌بام | برش‌کاران و حکاکان سنگ، بخش تولید | سنگ‌تراشان و سنگ‌چین‌ها | مجریان کف‌پوش‌های بتنی درجا و واش‌بتن (ترازو) | کاشی‌کاران و سنگ‌کاران ساختمانی</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | موکت‌کاران و نصابان فرش | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | ساب‌زنان و پرداخت‌کاران کف | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌ایزوگام‌کاران و کمک‌عایق‌کاران سقف | عایق‌کاران کف، سقف و دیوار | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | سفیدکاران و گچ‌کاران نما | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | سنگ‌شکنان و برش‌کاران سنگ معدن | عایق‌کاران و نصابان پوشش‌های سقفی | سنگ‌تراشان و حکاکان صنعتی سنگ | سنگ‌کاران ساختمانی | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ساختمان‌سازی و سازه | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | طراحی | مهندسی و فناوری</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | طراحی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | پایداری دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت جسمانی | دید نزدیک | دید دور | ادراک عمق | هماهنگی عمومی بدن | تعادل عمومی بدن | انعطاف‌پذیری دامنه حرکتی | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارگران ساختمانی | نجاران | سیمان‌کاران و پرداخت‌کاران بتن | بنایان و کارگران آجرچین و بلوک‌چین | سنگ‌تراشان و سنگ‌چین‌ها | سنگ‌فرش‌کاران و موزاییک‌ریزان قطعه‌ای | نصابان فنس و حصار | کارگران امحا و پاک‌سازی مواد خطرناک | کارگران نگهداری و راهداری بزرگراه‌ها | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | بازرسان ساختمان و ابنیه | نصابان و تکنسین‌های عایق‌کاری و بهسازی مصرف انرژی | عایق‌کاران کف، سقف و دیوار ساختمان | اپراتورهای ماشین‌آلات سنگین ساختمانی و مهندسی | کارگران سازه‌های فلزی و اسکلت فولادی | سقف‌کاران و عایق‌کاران پشت‌بام | شیشه‌بران و شیشه‌گذاران ساختمانی | نصابان ساختمان‌های پیش‌ساخته و کانکس | سرپرستان رده‌اول کارگران ساختمانی و استخراج معدن | سایر کارگران کمکی مشاغل ساختمانی</t>
+          <t>کارگران ساختمانی | نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | بنایان و سفت‌کاران ساختمان | سنگ‌کاران ساختمانی | سنگ‌فرش‌کاران و موزاییک‌ریزان قطعه‌ای | نصابان فنس و حصار | کارگران امحا و پاک‌سازی مواد خطرناک | کارگران راهداری و نگهداری جاده‌ها | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | بازرسان ساخت‌وساز و ساختمان | نصابان و تکنسین‌های عایق‌کاری و بهسازی مصرف انرژی | عایق‌کاران کف، سقف و دیوار | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اسکلت‌سازان و نصابان سازه‌های فولادی | عایق‌کاران و نصابان پوشش‌های سقفی | شیشه‌بران و نصابان شیشه | نصاب سازه‌های پیش‌ساخته و خانه‌های سیار | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | کمک‌کارگران سایر رشته‌های ساختمانی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ساختمان‌سازی و سازه | خدمات مشتریان و خدمات فردی | مکانیک | مدیریت و امور اداری | آموزش و تدریس | ریاضیات | زبان انگلیسی | ایمنی و امنیت عمومی | امور اداری و دفتری | رایانه و الکترونیک | اقتصاد و حسابداری | تولید و فرآوری | طراحی</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مکانیک | مدیریت و اداره | آموزش و پرورش | ریاضیات | زبان انگلیسی | ایمنی و امنیت عمومی | اداری | رایانه و الکترونیک | اقتصاد و حسابداری | تولید و فرآوری | طراحی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | چابکی دستی | درک شفاهی | بیان شفاهی | مرتب‌سازی اطلاعات | پایداری دست و بازو | هماهنگی چند عضو | تجسم فضایی | انعطاف‌پذیری بستار | ادراک عمق | دید دور | انعطاف‌پذیری دامنه حرکتی | قدرت تنه | وضوح گفتار | تشخیص گفتار | تشخیص تمایز رنگ‌ها | زمان واکنش | دقت کنترل | چابکی انگشتان | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | استدلال قیاسی | روانی ایده‌ها</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | مهارت دستی | درک شفاهی | بیان شفاهی | ترتیب‌دهی اطلاعات | ثبات دست و بازو | هماهنگی چند عضو | تجسم | انعطاف‌پذیری بستار | درک عمق | بینایی دور | انعطاف‌پذیری دامنه حرکت | قدرت تنه | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | زمان عکس‌العمل | دقت کنترل | مهارت انگشتان | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>دیگ‌سازان صنعتی | مدیران ساخت‌وساز و پروژه‌های عمرانی | بازرسان ساختمان و ابنیه | ممیزان انرژی | مهندسان انرژی، به‌جز باد و خورشید | تکنسین‌های سیستم‌های زمین‌گرمایی | مکانیک‌ها و نصابان سیستم‌های سرمایش، گرمایش و تهویه مطبوع | کارگران کمکی نصابان و تعمیرکاران | کارگران کمکی لوله‌کشان و تأسیسات‌کاران | عایق‌کاران کف، سقف و دیوار ساختمان | عایق‌کاران تأسیسات مکانیکی | کارگران نگهداری و تعمیرات عمومی | لوله‌کش‌ها و تأسیسات‌کاران خطوط بخار و پایپینگ | سقف‌کاران و عایق‌کاران پشت‌بام | سازندگان و ورق‌کاران فلزی | مدیران نصب سیستم‌های خورشیدی | نصابان سیستم‌های فتوولتائیک خورشیدی | نصابان و تکنسین‌های سیستم‌های حرارتی خورشیدی | مهندسان تأسیسات و اپراتورهای بویلر و دیگ‌های بخار | تکنسین‌های نگهداری و تعمیرات توربین بادی</t>
+          <t>دیگ‌سازان و مخزن‌سازان صنعتی | مدیران پروژه‌های ساختمانی | بازرسان ساخت‌وساز و ساختمان | ممیزان انرژی | مهندسان انرژی، به‌جز بادی و خورشیدی | تکنسین‌های سامانه‌های زمین‌گرمایی | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | کارگران عمومی تعمیرات و نگهداری تاسیسات | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | عایق‌کاران و نصابان پوشش‌های سقفی | کارگران ورق‌کاری فلزی | مدیران اجرای پروژه‌های انرژی خورشیدی | نصابان سیستم‌های خورشیدی فتوولتائیک | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
